--- a/data/workbooks/国内行业数据_0824.xlsx
+++ b/data/workbooks/国内行业数据_0824.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zeyichen\Desktop\IR_workbench\data\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\zeyichen\Desktop\IR_workbench\data\workbooks\aviation-pipeline-vxy5efu3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3B5A69-96BF-4AF0-A05A-3B07CCA62D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF96F6D3-FF25-4717-819B-93645C4F7757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5815,9 +5815,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="178" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -6857,7 +6857,7 @@
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6866,63 +6866,63 @@
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="401">
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6940,10 +6940,10 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6958,7 +6958,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6976,97 +6976,97 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="6" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="6" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="6" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="6" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="6" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7075,7 +7075,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7084,7 +7084,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7096,7 +7096,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7105,88 +7105,88 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="9" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="9" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="8" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="2" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7201,10 +7201,10 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="10" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="10" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7222,16 +7222,16 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="2" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7243,19 +7243,19 @@
     <xf numFmtId="9" fontId="4" fillId="10" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7267,22 +7267,22 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7303,7 +7303,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7318,40 +7318,40 @@
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="2" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7360,10 +7360,10 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7375,7 +7375,7 @@
     <xf numFmtId="9" fontId="4" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7384,13 +7384,13 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7405,7 +7405,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7432,34 +7432,34 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="2" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="5" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="50" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="51" xfId="3" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="49" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7471,19 +7471,19 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="52" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7504,37 +7504,37 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="11" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="7" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="7" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="7" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="7" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="7" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="11" fillId="7" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="7" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7546,28 +7546,28 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="55" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="13" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="13" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="13" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="13" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="13" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="13" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="13" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="13" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="13" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="13" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7582,64 +7582,64 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="13" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="13" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="14" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="2" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="4" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="16" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="16" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="16" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="16" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="16" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="14" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7651,7 +7651,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7669,13 +7669,13 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="15" fillId="2" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="15" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="15" fillId="2" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="15" fillId="2" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7702,13 +7702,13 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="15" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="6" fillId="15" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="15" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7723,7 +7723,7 @@
     <xf numFmtId="9" fontId="4" fillId="15" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="17" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="4" fillId="17" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7735,37 +7735,37 @@
     <xf numFmtId="9" fontId="4" fillId="17" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="18" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="3" fillId="18" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="18" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="18" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="18" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="18" borderId="56" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="18" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="18" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="18" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="18" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="18" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="18" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="18" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="18" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="18" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="18" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="18" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="18" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="18" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="18" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="17" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="17" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7780,7 +7780,7 @@
     <xf numFmtId="9" fontId="4" fillId="17" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="48" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7795,7 +7795,7 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="17" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="17" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7807,7 +7807,7 @@
     <xf numFmtId="9" fontId="4" fillId="17" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="17" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="17" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7822,7 +7822,7 @@
     <xf numFmtId="9" fontId="4" fillId="17" borderId="49" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="17" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="17" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7837,7 +7837,7 @@
     <xf numFmtId="9" fontId="4" fillId="17" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="17" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="17" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7861,13 +7861,13 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7884,114 +7884,6 @@
     </xf>
     <xf numFmtId="9" fontId="4" fillId="17" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="12" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="4" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="15" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="16" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="16" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="16" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="16" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="16" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="47" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8011,67 +7903,175 @@
     <xf numFmtId="9" fontId="4" fillId="2" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="16" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="16" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="16" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="16" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="16" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="15" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="41" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="12" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="5" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="5" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9011,17 +9011,17 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="338" t="s">
+      <c r="C2" s="375" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="338"/>
-      <c r="E2" s="338"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="375"/>
       <c r="F2" s="97"/>
-      <c r="G2" s="338" t="s">
+      <c r="G2" s="375" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="339"/>
-      <c r="I2" s="340"/>
+      <c r="H2" s="351"/>
+      <c r="I2" s="379"/>
       <c r="J2" s="99"/>
       <c r="K2" s="99"/>
       <c r="L2" s="99"/>
@@ -9031,30 +9031,30 @@
       <c r="R2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="338" t="s">
+      <c r="S2" s="375" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="338"/>
-      <c r="U2" s="338"/>
+      <c r="T2" s="375"/>
+      <c r="U2" s="375"/>
       <c r="V2" s="98"/>
-      <c r="W2" s="339" t="s">
+      <c r="W2" s="351" t="s">
         <v>5</v>
       </c>
-      <c r="X2" s="341"/>
-      <c r="Y2" s="342"/>
+      <c r="X2" s="352"/>
+      <c r="Y2" s="353"/>
       <c r="AA2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="338" t="s">
+      <c r="AB2" s="375" t="s">
         <v>6</v>
       </c>
-      <c r="AC2" s="338"/>
-      <c r="AD2" s="338"/>
+      <c r="AC2" s="375"/>
+      <c r="AD2" s="375"/>
       <c r="AE2" s="97"/>
-      <c r="AF2" s="339" t="s">
+      <c r="AF2" s="351" t="s">
         <v>5</v>
       </c>
-      <c r="AG2" s="343"/>
+      <c r="AG2" s="374"/>
       <c r="AH2" s="100"/>
     </row>
     <row r="3" spans="2:34" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -10144,11 +10144,11 @@
       </c>
       <c r="D17" s="129">
         <f>AVERAGE(D4:D6)</f>
-        <v>-0.17066666666666699</v>
+        <v>-0.17066666666666666</v>
       </c>
       <c r="E17" s="129">
         <f>AVERAGE(E4:E6)</f>
-        <v>-0.69666666666666699</v>
+        <v>-0.69666666666666666</v>
       </c>
       <c r="F17" s="129"/>
       <c r="G17" s="129">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="I17" s="130">
         <f>AVERAGE(I4:I6)</f>
-        <v>-0.52186025213199805</v>
+        <v>-0.52186025213199827</v>
       </c>
       <c r="J17" s="131"/>
       <c r="K17" s="131"/>
@@ -10220,15 +10220,15 @@
       </c>
       <c r="C18" s="129">
         <f>AVERAGE(C7:C9)</f>
-        <v>-0.38466666666666699</v>
+        <v>-0.38466666666666666</v>
       </c>
       <c r="D18" s="129">
         <f>AVERAGE(D7:D9)</f>
-        <v>-0.22233333333333299</v>
+        <v>-0.22233333333333336</v>
       </c>
       <c r="E18" s="129">
         <f>AVERAGE(E7:E9)</f>
-        <v>-0.51733333333333298</v>
+        <v>-0.51733333333333331</v>
       </c>
       <c r="F18" s="129"/>
       <c r="G18" s="129">
@@ -10302,11 +10302,11 @@
       </c>
       <c r="C19" s="129">
         <f>AVERAGE(C10:C12)</f>
-        <v>-0.100333333333333</v>
+        <v>-0.10033333333333334</v>
       </c>
       <c r="D19" s="129">
         <f>AVERAGE(D10:D12)</f>
-        <v>-6.7333333333333301E-2</v>
+        <v>-6.7333333333333328E-2</v>
       </c>
       <c r="E19" s="129">
         <f>AVERAGE(E10:E12)</f>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="I19" s="130">
         <f>AVERAGE(I10:I12)</f>
-        <v>-0.14124444444444501</v>
+        <v>-0.14124444444444456</v>
       </c>
       <c r="J19" s="131"/>
       <c r="K19" s="131"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="C20" s="136">
         <f>AVERAGE(C13:C15)</f>
-        <v>-7.8666666666666704E-2</v>
+        <v>-7.8666666666666663E-2</v>
       </c>
       <c r="D20" s="136">
         <f>AVERAGE(D13:D15)</f>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="E20" s="136">
         <f>AVERAGE(E13:E15)</f>
-        <v>-0.12466666666666699</v>
+        <v>-0.12466666666666666</v>
       </c>
       <c r="F20" s="137"/>
       <c r="G20" s="138">
@@ -10470,15 +10470,15 @@
       </c>
       <c r="C21" s="145">
         <f>AVERAGE(C4:C15)</f>
-        <v>-0.301416666666667</v>
+        <v>-0.30141666666666667</v>
       </c>
       <c r="D21" s="145">
         <f>AVERAGE(D4:D15)</f>
-        <v>-0.12783333333333299</v>
+        <v>-0.12783333333333333</v>
       </c>
       <c r="E21" s="145">
         <f>AVERAGE(E4:E15)</f>
-        <v>-0.37441666666666701</v>
+        <v>-0.37441666666666662</v>
       </c>
       <c r="F21" s="145" t="e">
         <f>AVERAGE(F4:F15)</f>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="I21" s="145">
         <f>AVERAGE(I4:I15)</f>
-        <v>-0.30216004542083802</v>
+        <v>-0.30216004542083791</v>
       </c>
       <c r="J21" s="146"/>
       <c r="K21" s="146"/>
@@ -10513,11 +10513,11 @@
       </c>
       <c r="T21" s="145">
         <f>AVERAGE(T4:T15)</f>
-        <v>-5.83611111111111E-2</v>
+        <v>-5.8361111111111114E-2</v>
       </c>
       <c r="U21" s="145">
         <f>AVERAGE(U4:U15)</f>
-        <v>-0.25895833333333301</v>
+        <v>-0.25895833333333335</v>
       </c>
       <c r="V21" s="145"/>
       <c r="W21" s="145">
@@ -10610,35 +10610,35 @@
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="338" t="s">
+      <c r="C24" s="375" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="338"/>
-      <c r="E24" s="338"/>
+      <c r="D24" s="375"/>
+      <c r="E24" s="375"/>
       <c r="F24" s="154"/>
-      <c r="G24" s="344" t="s">
+      <c r="G24" s="376" t="s">
         <v>60</v>
       </c>
-      <c r="H24" s="345"/>
+      <c r="H24" s="377"/>
       <c r="I24" s="155" t="s">
         <v>61</v>
       </c>
       <c r="J24" s="4"/>
-      <c r="K24" s="346" t="s">
+      <c r="K24" s="378" t="s">
         <v>62</v>
       </c>
-      <c r="L24" s="342"/>
+      <c r="L24" s="353"/>
       <c r="M24" s="99"/>
       <c r="N24" s="99"/>
       <c r="O24" s="156"/>
       <c r="R24" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="347" t="s">
+      <c r="S24" s="362" t="s">
         <v>63</v>
       </c>
-      <c r="T24" s="348"/>
-      <c r="U24" s="349"/>
+      <c r="T24" s="363"/>
+      <c r="U24" s="364"/>
       <c r="V24" s="7"/>
       <c r="W24" s="13" t="s">
         <v>5</v>
@@ -11561,15 +11561,15 @@
       <c r="D45" s="188"/>
       <c r="E45" s="188"/>
       <c r="F45" s="188"/>
-      <c r="G45" s="350"/>
-      <c r="H45" s="350"/>
-      <c r="I45" s="350"/>
+      <c r="G45" s="369"/>
+      <c r="H45" s="369"/>
+      <c r="I45" s="369"/>
       <c r="J45" s="188"/>
-      <c r="K45" s="351" t="s">
+      <c r="K45" s="370" t="s">
         <v>86</v>
       </c>
-      <c r="L45" s="351"/>
-      <c r="M45" s="351"/>
+      <c r="L45" s="370"/>
+      <c r="M45" s="370"/>
       <c r="N45" s="189"/>
       <c r="O45" s="188"/>
       <c r="P45" s="188"/>
@@ -11605,24 +11605,24 @@
       <c r="B46" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="352" t="s">
+      <c r="C46" s="371" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="352"/>
-      <c r="E46" s="352"/>
+      <c r="D46" s="371"/>
+      <c r="E46" s="371"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="353" t="s">
+      <c r="G46" s="360" t="s">
         <v>60</v>
       </c>
-      <c r="H46" s="354"/>
+      <c r="H46" s="361"/>
       <c r="I46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J46" s="4"/>
-      <c r="K46" s="355" t="s">
+      <c r="K46" s="372" t="s">
         <v>62</v>
       </c>
-      <c r="L46" s="356"/>
+      <c r="L46" s="373"/>
       <c r="M46" s="190" t="s">
         <v>89</v>
       </c>
@@ -11630,11 +11630,11 @@
       <c r="R46" s="192" t="s">
         <v>90</v>
       </c>
-      <c r="S46" s="357" t="s">
+      <c r="S46" s="366" t="s">
         <v>63</v>
       </c>
-      <c r="T46" s="357"/>
-      <c r="U46" s="357"/>
+      <c r="T46" s="366"/>
+      <c r="U46" s="366"/>
       <c r="V46" s="7"/>
       <c r="W46" s="159" t="s">
         <v>91</v>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="M48" s="20">
         <f>65.8%-1</f>
-        <v>-0.34200000000000003</v>
+        <v>-0.34200000000000008</v>
       </c>
       <c r="N48" s="21"/>
       <c r="R48" s="111" t="s">
@@ -11800,10 +11800,10 @@
         <v>-0.14371897345745299</v>
       </c>
       <c r="AF48" s="25"/>
-      <c r="AG48" s="374" t="s">
+      <c r="AG48" s="338" t="s">
         <v>99</v>
       </c>
-      <c r="AH48" s="377" t="s">
+      <c r="AH48" s="341" t="s">
         <v>100</v>
       </c>
     </row>
@@ -11874,8 +11874,8 @@
         <v>2.73818897665297E-2</v>
       </c>
       <c r="AF49" s="25"/>
-      <c r="AG49" s="375"/>
-      <c r="AH49" s="378"/>
+      <c r="AG49" s="339"/>
+      <c r="AH49" s="342"/>
     </row>
     <row r="50" spans="2:34" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B50" s="23" t="s">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="M50" s="20">
         <f>69.7%-1</f>
-        <v>-0.30299999999999999</v>
+        <v>-0.30299999999999994</v>
       </c>
       <c r="N50" s="21"/>
       <c r="R50" s="111" t="s">
@@ -11946,8 +11946,8 @@
         <v>-0.21150047657135501</v>
       </c>
       <c r="AF50" s="25"/>
-      <c r="AG50" s="375"/>
-      <c r="AH50" s="378"/>
+      <c r="AG50" s="339"/>
+      <c r="AH50" s="342"/>
     </row>
     <row r="51" spans="2:34" ht="14" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B51" s="23" t="s">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="M51" s="193">
         <f>71%-1</f>
-        <v>-0.28999999999999998</v>
+        <v>-0.29000000000000004</v>
       </c>
       <c r="N51" s="21"/>
       <c r="R51" s="111" t="s">
@@ -12018,8 +12018,8 @@
         <v>0.48101512282699299</v>
       </c>
       <c r="AF51" s="25"/>
-      <c r="AG51" s="375"/>
-      <c r="AH51" s="378"/>
+      <c r="AG51" s="339"/>
+      <c r="AH51" s="342"/>
     </row>
     <row r="52" spans="2:34" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B52" s="23" t="s">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="M52" s="193">
         <f>72.4%-1</f>
-        <v>-0.27600000000000002</v>
+        <v>-0.27599999999999991</v>
       </c>
       <c r="N52" s="21"/>
       <c r="R52" s="111" t="s">
@@ -12088,8 +12088,8 @@
         <v>-0.288116863921768</v>
       </c>
       <c r="AF52" s="25"/>
-      <c r="AG52" s="375"/>
-      <c r="AH52" s="378"/>
+      <c r="AG52" s="339"/>
+      <c r="AH52" s="342"/>
     </row>
     <row r="53" spans="2:34" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B53" s="15" t="s">
@@ -12160,8 +12160,8 @@
         <v>-0.114</v>
       </c>
       <c r="AF53" s="25"/>
-      <c r="AG53" s="375"/>
-      <c r="AH53" s="378"/>
+      <c r="AG53" s="339"/>
+      <c r="AH53" s="342"/>
     </row>
     <row r="54" spans="2:34" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B54" s="15" t="s">
@@ -12227,8 +12227,8 @@
         <v>-8.0348090124015906E-2</v>
       </c>
       <c r="AF54" s="25"/>
-      <c r="AG54" s="376"/>
-      <c r="AH54" s="379"/>
+      <c r="AG54" s="340"/>
+      <c r="AH54" s="343"/>
     </row>
     <row r="55" spans="2:34" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B55" s="15" t="s">
@@ -12632,15 +12632,15 @@
       </c>
       <c r="C61" s="25">
         <f>AVERAGE(C48:C50)</f>
-        <v>2.6346097682150599E-2</v>
+        <v>2.6346097682150571E-2</v>
       </c>
       <c r="D61" s="25">
         <f>AVERAGE(D48:D50)</f>
-        <v>1.2644605886939501E-2</v>
+        <v>1.2644605886939527E-2</v>
       </c>
       <c r="E61" s="25">
         <f>AVERAGE(E48:E50)</f>
-        <v>1.7237019739619101E-2</v>
+        <v>1.7237019739619129E-2</v>
       </c>
       <c r="F61" s="26"/>
       <c r="G61" s="27">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="M61" s="28">
         <f>AVERAGE(M48:M50)</f>
-        <v>-0.30733333333333301</v>
+        <v>-0.30733333333333335</v>
       </c>
       <c r="N61" s="32"/>
       <c r="AB61" s="111" t="s">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="E62" s="25">
         <f t="shared" si="0"/>
-        <v>-8.5330349774372399E-2</v>
+        <v>-8.5330349774372372E-2</v>
       </c>
       <c r="F62" s="26"/>
       <c r="G62" s="27" t="e">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="M62" s="28">
         <f>AVERAGE(M51:M53)</f>
-        <v>-0.27800000000000002</v>
+        <v>-0.27799999999999997</v>
       </c>
       <c r="N62" s="32"/>
       <c r="AB62" s="202" t="s">
@@ -12758,33 +12758,33 @@
       </c>
       <c r="C63" s="25">
         <f>AVERAGE(C54:C56)</f>
-        <v>-1.6666666666666701E-2</v>
+        <v>-1.6666666666666666E-2</v>
       </c>
       <c r="D63" s="25">
         <f>AVERAGE(D54:D56)</f>
-        <v>-7.5333333333333294E-2</v>
+        <v>-7.5333333333333335E-2</v>
       </c>
       <c r="E63" s="25">
         <f>AVERAGE(E54:E56)</f>
-        <v>-9.1999999999999998E-2</v>
+        <v>-9.2000000000000012E-2</v>
       </c>
       <c r="F63" s="26"/>
       <c r="G63" s="27">
         <f>AVERAGE(G54:G56)</f>
-        <v>8.23333333333333E-2</v>
+        <v>8.2333333333333328E-2</v>
       </c>
       <c r="H63" s="26">
         <f>AVERAGE(H54:H56)</f>
-        <v>8.6666666666666697E-2</v>
+        <v>8.666666666666667E-2</v>
       </c>
       <c r="I63" s="28">
         <f>AVERAGE(I54:I56)</f>
-        <v>6.63333333333333E-2</v>
+        <v>6.6333333333333341E-2</v>
       </c>
       <c r="J63" s="32"/>
       <c r="K63" s="25">
         <f>AVERAGE(K54:K56)</f>
-        <v>-7.36666666666667E-2</v>
+        <v>-7.3666666666666672E-2</v>
       </c>
       <c r="L63" s="26">
         <f>AVERAGE(L54:L56)</f>
@@ -12792,7 +12792,7 @@
       </c>
       <c r="M63" s="28">
         <f>AVERAGE(M54:M56)</f>
-        <v>-0.21466666666666701</v>
+        <v>-0.21466666666666667</v>
       </c>
       <c r="N63" s="32"/>
       <c r="AB63" s="111" t="s">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="C64" s="140">
         <f>AVERAGE(C57:C59)</f>
-        <v>-1.36666666666667E-2</v>
+        <v>-1.3666666666666666E-2</v>
       </c>
       <c r="D64" s="140">
         <f>AVERAGE(D57:D59)</f>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="E64" s="140">
         <f>AVERAGE(E57:E59)</f>
-        <v>-4.8000000000000001E-2</v>
+        <v>-4.7999999999999994E-2</v>
       </c>
       <c r="F64" s="175"/>
       <c r="G64" s="176">
@@ -12835,11 +12835,11 @@
       </c>
       <c r="H64" s="205">
         <f>AVERAGE(H57:H59)</f>
-        <v>7.6666666666666702E-2</v>
+        <v>7.6666666666666661E-2</v>
       </c>
       <c r="I64" s="206">
         <f>AVERAGE(I57:I59)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>5.7999999999999996E-2</v>
       </c>
       <c r="J64" s="207"/>
       <c r="K64" s="140">
@@ -12847,11 +12847,11 @@
       </c>
       <c r="L64" s="205">
         <f>AVERAGE(L57:L59)</f>
-        <v>2.33333333333333E-2</v>
+        <v>2.3333333333333334E-2</v>
       </c>
       <c r="M64" s="206">
         <f>AVERAGE(M57:M59)</f>
-        <v>-0.209666666666667</v>
+        <v>-0.20966666666666667</v>
       </c>
       <c r="N64" s="32"/>
       <c r="AB64" s="111" t="s">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="E65" s="140">
         <f>AVERAGE(E61:E64)</f>
-        <v>-5.2023332508688298E-2</v>
+        <v>-5.2023332508688305E-2</v>
       </c>
       <c r="F65" s="175" t="e">
         <f t="shared" ref="F65:M65" si="1">AVERAGE(F61:F64)</f>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="I65" s="208">
         <f t="shared" si="1"/>
-        <v>0.12789804017505199</v>
+        <v>0.12789804017505235</v>
       </c>
       <c r="J65" s="31" t="e">
         <f t="shared" si="1"/>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="M65" s="206">
         <f t="shared" si="1"/>
-        <v>-0.25241666666666701</v>
+        <v>-0.25241666666666662</v>
       </c>
       <c r="N65" s="32"/>
       <c r="AB65" s="111"/>
@@ -12971,10 +12971,10 @@
       <c r="B69" s="211"/>
       <c r="I69" s="111"/>
       <c r="J69" s="111"/>
-      <c r="K69" s="358" t="s">
+      <c r="K69" s="367" t="s">
         <v>62</v>
       </c>
-      <c r="L69" s="359"/>
+      <c r="L69" s="368"/>
       <c r="M69" s="32"/>
       <c r="N69" s="32"/>
       <c r="AB69" s="111"/>
@@ -13125,24 +13125,24 @@
       <c r="B74" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C74" s="360" t="s">
+      <c r="C74" s="357" t="s">
         <v>6</v>
       </c>
-      <c r="D74" s="361"/>
-      <c r="E74" s="362"/>
+      <c r="D74" s="358"/>
+      <c r="E74" s="359"/>
       <c r="F74" s="2"/>
-      <c r="G74" s="353" t="s">
+      <c r="G74" s="360" t="s">
         <v>60</v>
       </c>
-      <c r="H74" s="354"/>
+      <c r="H74" s="361"/>
       <c r="I74" s="56" t="s">
         <v>61</v>
       </c>
       <c r="J74" s="4"/>
-      <c r="K74" s="363" t="s">
+      <c r="K74" s="349" t="s">
         <v>62</v>
       </c>
-      <c r="L74" s="364"/>
+      <c r="L74" s="350"/>
       <c r="M74" s="5" t="s">
         <v>89</v>
       </c>
@@ -13152,11 +13152,11 @@
       <c r="R74" s="192" t="s">
         <v>138</v>
       </c>
-      <c r="S74" s="347" t="s">
+      <c r="S74" s="362" t="s">
         <v>63</v>
       </c>
-      <c r="T74" s="348"/>
-      <c r="U74" s="349"/>
+      <c r="T74" s="363"/>
+      <c r="U74" s="364"/>
       <c r="V74" s="7"/>
       <c r="W74" s="159" t="s">
         <v>91</v>
@@ -13287,7 +13287,7 @@
       </c>
       <c r="M76" s="22">
         <f>92.4%-100%</f>
-        <v>-7.5999999999999998E-2</v>
+        <v>-7.5999999999999956E-2</v>
       </c>
       <c r="N76" s="21">
         <v>-0.12</v>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="M78" s="22">
         <f>0.855-1</f>
-        <v>-0.14499999999999999</v>
+        <v>-0.14500000000000002</v>
       </c>
       <c r="N78" s="21">
         <v>-0.2</v>
@@ -13503,7 +13503,7 @@
       </c>
       <c r="M79" s="22">
         <f>0.891-1</f>
-        <v>-0.109</v>
+        <v>-0.10899999999999999</v>
       </c>
       <c r="N79" s="21">
         <v>-0.16</v>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="M80" s="22">
         <f>87.6%-1</f>
-        <v>-0.124</v>
+        <v>-0.12400000000000011</v>
       </c>
       <c r="N80" s="21">
         <v>-0.18</v>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="E81" s="119">
         <f>AVERAGE(U99:U102)</f>
-        <v>-8.1000000000000003E-2</v>
+        <v>-8.0999999999999989E-2</v>
       </c>
       <c r="F81" s="168"/>
       <c r="G81" s="169">
@@ -13705,11 +13705,11 @@
       </c>
       <c r="D82" s="119">
         <f>AVERAGE(T103:T107)</f>
-        <v>-1.5599999999999999E-2</v>
+        <v>-1.5599999999999998E-2</v>
       </c>
       <c r="E82" s="119">
         <f>AVERAGE(U103:U107)</f>
-        <v>-5.9619999999999999E-2</v>
+        <v>-5.9619999999999992E-2</v>
       </c>
       <c r="F82" s="168"/>
       <c r="G82" s="169">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="M82" s="22">
         <f>89.1%-1</f>
-        <v>-0.109</v>
+        <v>-0.1090000000000001</v>
       </c>
       <c r="N82" s="21">
         <v>-0.15</v>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="D83" s="119">
         <f>AVERAGE(T108:T111)</f>
-        <v>-2.2499999999999999E-2</v>
+        <v>-2.2500000000000003E-2</v>
       </c>
       <c r="E83" s="119">
         <f>AVERAGE(U108:U111)</f>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="M83" s="22">
         <f>88.6%-1</f>
-        <v>-0.114</v>
+        <v>-0.1140000000000001</v>
       </c>
       <c r="N83" s="21"/>
       <c r="R83" s="221" t="s">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="C84" s="119">
         <f>AVERAGE(S112:S115)</f>
-        <v>-2.4999999999999301E-4</v>
+        <v>-2.4999999999999328E-4</v>
       </c>
       <c r="D84" s="119">
         <f>AVERAGE(T112:T115)</f>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="E84" s="119">
         <f>AVERAGE(U112:U115)</f>
-        <v>9.75E-3</v>
+        <v>9.7499999999999965E-3</v>
       </c>
       <c r="F84" s="168"/>
       <c r="G84" s="169">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="M84" s="22">
         <f>85.7%-1</f>
-        <v>-0.14299999999999999</v>
+        <v>-0.14300000000000002</v>
       </c>
       <c r="N84" s="21"/>
       <c r="R84" s="111" t="s">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="M85" s="22">
         <f>90%-1</f>
-        <v>-0.1</v>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="N85" s="21"/>
       <c r="R85" s="111" t="s">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="D86" s="119">
         <f t="shared" ref="D86:E86" si="2">AVERAGE(T121:T124)</f>
-        <v>3.7499999999999999E-2</v>
+        <v>3.7500000000000006E-2</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="2"/>
@@ -14018,7 +14018,7 @@
       </c>
       <c r="M86" s="22">
         <f>85.8%-1</f>
-        <v>-0.14199999999999999</v>
+        <v>-0.14200000000000002</v>
       </c>
       <c r="N86" s="21"/>
       <c r="R86" s="111" t="s">
@@ -14066,11 +14066,11 @@
       </c>
       <c r="D87" s="119">
         <f t="shared" ref="D87:E87" si="3">AVERAGE(T125:T129)</f>
-        <v>0.06</v>
+        <v>6.0000000000000012E-2</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="3"/>
-        <v>5.8000000000000003E-2</v>
+        <v>5.7999999999999996E-2</v>
       </c>
       <c r="F87" s="168"/>
       <c r="G87" s="223">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="M87" s="67">
         <f>84.4%-1</f>
-        <v>-0.156</v>
+        <v>-0.15599999999999992</v>
       </c>
       <c r="N87" s="21"/>
       <c r="R87" s="111" t="s">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="C89" s="25">
         <f>AVERAGE(C76:C78)</f>
-        <v>1.6666666666666701E-2</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="D89" s="25">
         <f>AVERAGE(D76:D78)</f>
@@ -14194,37 +14194,37 @@
       </c>
       <c r="E89" s="25">
         <f>AVERAGE(E76:E78)</f>
-        <v>-5.6666666666666698E-2</v>
+        <v>-5.6666666666666664E-2</v>
       </c>
       <c r="F89" s="232"/>
       <c r="G89" s="233">
         <f>AVERAGE(G76:G78)</f>
-        <v>3.3333333333333298E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="H89" s="25">
         <f>AVERAGE(H76:H78)</f>
-        <v>1.3333333333333299E-2</v>
+        <v>1.3333333333333336E-2</v>
       </c>
       <c r="I89" s="234">
         <f>AVERAGE(I76:I78)</f>
-        <v>6.0666666666666702E-2</v>
+        <v>6.0666666666666667E-2</v>
       </c>
       <c r="J89" s="235"/>
       <c r="K89" s="233">
         <f>AVERAGE(K76:K78)</f>
-        <v>3.3333333333333301E-3</v>
+        <v>3.3333333333333318E-3</v>
       </c>
       <c r="L89" s="25">
         <f>AVERAGE(L76:L78)</f>
-        <v>3.3333333333333301E-3</v>
+        <v>3.3333333333333327E-3</v>
       </c>
       <c r="M89" s="234">
         <f>AVERAGE(M76:M78)</f>
-        <v>-0.119333333333333</v>
+        <v>-0.11933333333333333</v>
       </c>
       <c r="N89" s="32">
         <f>AVERAGE(N76:N78)</f>
-        <v>-0.15666666666666701</v>
+        <v>-0.15666666666666668</v>
       </c>
       <c r="R89" s="111" t="s">
         <v>170</v>
@@ -14271,20 +14271,20 @@
       </c>
       <c r="D90" s="25">
         <f>AVERAGE(D79:D81)</f>
-        <v>-6.0916666666666702E-2</v>
+        <v>-6.0916666666666668E-2</v>
       </c>
       <c r="E90" s="25">
         <f>AVERAGE(E79:E81)</f>
-        <v>-9.0333333333333293E-2</v>
+        <v>-9.0333333333333335E-2</v>
       </c>
       <c r="F90" s="30"/>
       <c r="G90" s="25">
         <f>AVERAGE(G79:G81)</f>
-        <v>5.6666666666666698E-2</v>
+        <v>5.6666666666666671E-2</v>
       </c>
       <c r="H90" s="25">
         <f>AVERAGE(H79:H81)</f>
-        <v>5.3333333333333302E-2</v>
+        <v>5.3333333333333337E-2</v>
       </c>
       <c r="I90" s="30">
         <f>AVERAGE(I79:I81)</f>
@@ -14293,7 +14293,7 @@
       <c r="J90" s="31"/>
       <c r="K90" s="233">
         <f>AVERAGE(K79:K81)</f>
-        <v>1.3333333333333299E-2</v>
+        <v>1.3333333333333334E-2</v>
       </c>
       <c r="L90" s="25">
         <f>AVERAGE(L79:L81)</f>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="M90" s="30">
         <f>AVERAGE(M79:M81)</f>
-        <v>-0.12066666666666701</v>
+        <v>-0.1206666666666667</v>
       </c>
       <c r="N90" s="32">
         <f>AVERAGE(N79:N81)</f>
@@ -14331,11 +14331,11 @@
       </c>
       <c r="C91" s="25">
         <f>AVERAGE(C82:C84)</f>
-        <v>-1.9103333333333299E-2</v>
+        <v>-1.910333333333333E-2</v>
       </c>
       <c r="D91" s="25">
         <f>AVERAGE(D82:D84)</f>
-        <v>-1.00333333333333E-2</v>
+        <v>-1.0033333333333333E-2</v>
       </c>
       <c r="E91" s="25">
         <f>AVERAGE(E82:E84)</f>
@@ -14348,16 +14348,16 @@
       </c>
       <c r="H91" s="26">
         <f>AVERAGE(H82:H84)</f>
-        <v>2.66666666666667E-2</v>
+        <v>2.6666666666666668E-2</v>
       </c>
       <c r="I91" s="30">
         <f>AVERAGE(I82:I84)</f>
-        <v>4.2999999999999997E-2</v>
+        <v>4.3000000000000003E-2</v>
       </c>
       <c r="J91" s="32"/>
       <c r="K91" s="27">
         <f>AVERAGE(K82:K84)</f>
-        <v>4.6666666666666697E-2</v>
+        <v>4.6666666666666669E-2</v>
       </c>
       <c r="L91" s="26">
         <f>AVERAGE(L82:L84)</f>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="M91" s="30">
         <f>AVERAGE(M82:M84)</f>
-        <v>-0.122</v>
+        <v>-0.12200000000000007</v>
       </c>
       <c r="N91" s="32"/>
       <c r="R91" s="111" t="s">
@@ -14396,29 +14396,29 @@
       </c>
       <c r="D92" s="140">
         <f t="shared" ref="D92:E92" si="4">AVERAGE(D85:D87)</f>
-        <v>5.2166666666666701E-2</v>
+        <v>5.2166666666666674E-2</v>
       </c>
       <c r="E92" s="140">
         <f t="shared" si="4"/>
-        <v>3.6266666666666697E-2</v>
+        <v>3.6266666666666662E-2</v>
       </c>
       <c r="F92" s="236"/>
       <c r="G92" s="176">
         <f>AVERAGE(G85:G87)</f>
-        <v>0.05</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="H92" s="205">
         <f>AVERAGE(H85:H87)</f>
-        <v>5.3333333333333302E-2</v>
+        <v>5.3333333333333337E-2</v>
       </c>
       <c r="I92" s="142">
         <f>AVERAGE(I85:I87)</f>
-        <v>9.1666666666666702E-2</v>
+        <v>9.1666666666666674E-2</v>
       </c>
       <c r="J92" s="207"/>
       <c r="K92" s="176">
         <f>AVERAGE(K85:K87)</f>
-        <v>0.12666666666666701</v>
+        <v>0.12666666666666668</v>
       </c>
       <c r="L92" s="205">
         <f>AVERAGE(L85:L87)</f>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="M92" s="142">
         <f>AVERAGE(M85:M87)</f>
-        <v>-0.13266666666666699</v>
+        <v>-0.13266666666666663</v>
       </c>
       <c r="N92" s="32"/>
       <c r="R92" s="111" t="s">
@@ -15407,24 +15407,24 @@
       <c r="B136" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C136" s="360" t="s">
+      <c r="C136" s="357" t="s">
         <v>6</v>
       </c>
-      <c r="D136" s="361"/>
-      <c r="E136" s="362"/>
+      <c r="D136" s="358"/>
+      <c r="E136" s="359"/>
       <c r="F136" s="2"/>
-      <c r="G136" s="353" t="s">
+      <c r="G136" s="360" t="s">
         <v>60</v>
       </c>
-      <c r="H136" s="354"/>
+      <c r="H136" s="361"/>
       <c r="I136" s="56" t="s">
         <v>61</v>
       </c>
       <c r="J136" s="4"/>
-      <c r="K136" s="363" t="s">
+      <c r="K136" s="349" t="s">
         <v>62</v>
       </c>
-      <c r="L136" s="364"/>
+      <c r="L136" s="350"/>
       <c r="M136" s="5" t="s">
         <v>89</v>
       </c>
@@ -15434,11 +15434,11 @@
       <c r="R136" s="192" t="s">
         <v>138</v>
       </c>
-      <c r="S136" s="347" t="s">
+      <c r="S136" s="362" t="s">
         <v>63</v>
       </c>
-      <c r="T136" s="348"/>
-      <c r="U136" s="349"/>
+      <c r="T136" s="363"/>
+      <c r="U136" s="364"/>
       <c r="V136" s="7"/>
       <c r="W136" s="159" t="s">
         <v>91</v>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="N151" s="32">
         <f>AVERAGE(N138:N140)</f>
-        <v>-0.15666666666666701</v>
+        <v>-0.15666666666666668</v>
       </c>
       <c r="R151" s="241" t="s">
         <v>185</v>
@@ -16653,24 +16653,24 @@
       <c r="B166" s="248" t="s">
         <v>221</v>
       </c>
-      <c r="C166" s="366" t="s">
+      <c r="C166" s="344" t="s">
         <v>6</v>
       </c>
-      <c r="D166" s="367"/>
-      <c r="E166" s="368"/>
+      <c r="D166" s="345"/>
+      <c r="E166" s="346"/>
       <c r="F166" s="249"/>
-      <c r="G166" s="369" t="s">
+      <c r="G166" s="347" t="s">
         <v>222</v>
       </c>
-      <c r="H166" s="370"/>
+      <c r="H166" s="348"/>
       <c r="I166" s="250" t="s">
         <v>61</v>
       </c>
       <c r="J166" s="4"/>
-      <c r="K166" s="363" t="s">
+      <c r="K166" s="349" t="s">
         <v>223</v>
       </c>
-      <c r="L166" s="364"/>
+      <c r="L166" s="350"/>
       <c r="M166" s="251" t="s">
         <v>89</v>
       </c>
@@ -16680,17 +16680,17 @@
       <c r="R166" s="252" t="s">
         <v>224</v>
       </c>
-      <c r="S166" s="339" t="s">
+      <c r="S166" s="351" t="s">
         <v>63</v>
       </c>
-      <c r="T166" s="341"/>
-      <c r="U166" s="342"/>
+      <c r="T166" s="352"/>
+      <c r="U166" s="353"/>
       <c r="V166" s="158"/>
-      <c r="W166" s="371" t="s">
+      <c r="W166" s="354" t="s">
         <v>225</v>
       </c>
-      <c r="X166" s="372"/>
-      <c r="Y166" s="373"/>
+      <c r="X166" s="355"/>
+      <c r="Y166" s="356"/>
       <c r="Z166" s="160" t="s">
         <v>64</v>
       </c>
@@ -16763,15 +16763,15 @@
       </c>
       <c r="C168" s="16">
         <f>AVERAGE(S168:S171)</f>
-        <v>3.5882529500654903E-2</v>
+        <v>3.5882529500654931E-2</v>
       </c>
       <c r="D168" s="16">
         <f t="shared" ref="D168:E168" si="5">AVERAGE(T168:T171)</f>
-        <v>-0.12673754541455201</v>
+        <v>-0.1267375454145524</v>
       </c>
       <c r="E168" s="16">
         <f t="shared" si="5"/>
-        <v>-0.10616404685153601</v>
+        <v>-0.10616404685153624</v>
       </c>
       <c r="F168" s="17"/>
       <c r="G168" s="18">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="M168" s="22">
         <f>89.6%-1</f>
-        <v>-0.104</v>
+        <v>-0.10400000000000009</v>
       </c>
       <c r="N168" s="21">
         <v>-0.12</v>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="M169" s="22">
         <f>93.2%-1</f>
-        <v>-6.7999999999999894E-2</v>
+        <v>-6.7999999999999949E-2</v>
       </c>
       <c r="N169" s="21">
         <v>-0.15</v>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="M170" s="67">
         <f>89.4%-1</f>
-        <v>-0.106</v>
+        <v>-0.10599999999999998</v>
       </c>
       <c r="N170" s="21">
         <v>-0.2</v>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="M171" s="265">
         <f>89.3%-1</f>
-        <v>-0.107</v>
+        <v>-0.10699999999999998</v>
       </c>
       <c r="N171" s="21">
         <v>-0.16</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="M172" s="271">
         <f>85%-1</f>
-        <v>-0.15</v>
+        <v>-0.15000000000000002</v>
       </c>
       <c r="N172" s="21">
         <v>-0.18</v>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="M173" s="82">
         <f>83.7%-1</f>
-        <v>-0.16300000000000001</v>
+        <v>-0.16299999999999992</v>
       </c>
       <c r="N173" s="21">
         <v>-0.17</v>
@@ -17143,12 +17143,20 @@
         <v>-3.9600000000000003E-2</v>
       </c>
       <c r="F174" s="168"/>
-      <c r="G174" s="169"/>
-      <c r="H174" s="121"/>
+      <c r="G174" s="169">
+        <v>4.089905930598392E-2</v>
+      </c>
+      <c r="H174" s="121">
+        <v>5.3006848524479233E-2</v>
+      </c>
       <c r="I174" s="22"/>
       <c r="J174" s="21"/>
-      <c r="K174" s="169"/>
-      <c r="L174" s="121"/>
+      <c r="K174" s="169">
+        <v>2.458396369137672E-2</v>
+      </c>
+      <c r="L174" s="121">
+        <v>6.0466022394113361E-2</v>
+      </c>
       <c r="M174" s="22"/>
       <c r="N174" s="21">
         <v>-0.15</v>
@@ -17436,7 +17444,7 @@
       </c>
       <c r="I181" s="234">
         <f>AVERAGE(I168:I170)</f>
-        <v>5.6666666666666698E-2</v>
+        <v>5.6666666666666671E-2</v>
       </c>
       <c r="J181" s="235"/>
       <c r="K181" s="233">
@@ -17453,7 +17461,7 @@
       </c>
       <c r="N181" s="32">
         <f>AVERAGE(N168:N170)</f>
-        <v>-0.15666666666666701</v>
+        <v>-0.15666666666666668</v>
       </c>
       <c r="R181" s="23" t="s">
         <v>244</v>
@@ -17485,15 +17493,15 @@
       </c>
       <c r="C182" s="285">
         <f>AVERAGE(C171:C173)</f>
-        <v>-8.3333333333333297E-3</v>
+        <v>-8.3333333333333332E-3</v>
       </c>
       <c r="D182" s="285">
         <f>AVERAGE(D171:D173)</f>
-        <v>2.9000000000000001E-2</v>
+        <v>2.8999999999999998E-2</v>
       </c>
       <c r="E182" s="285">
         <f>AVERAGE(E171:E173)</f>
-        <v>2.0333333333333301E-2</v>
+        <v>2.0333333333333332E-2</v>
       </c>
       <c r="F182" s="286"/>
       <c r="G182" s="285">
@@ -17514,7 +17522,7 @@
       </c>
       <c r="M182" s="286">
         <f>AVERAGE(M171:M173)</f>
-        <v>-0.14000000000000001</v>
+        <v>-0.13999999999999999</v>
       </c>
       <c r="N182" s="32">
         <f>AVERAGE(N171:N173)</f>
@@ -18370,6 +18378,27 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="33">
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="S24:U24"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="S46:U46"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="S74:U74"/>
     <mergeCell ref="AG48:AG54"/>
     <mergeCell ref="AH48:AH54"/>
     <mergeCell ref="C166:E166"/>
@@ -18382,27 +18411,6 @@
     <mergeCell ref="K136:L136"/>
     <mergeCell ref="S136:U136"/>
     <mergeCell ref="K165:L165"/>
-    <mergeCell ref="S46:U46"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="S74:U74"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="S2:U2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="AB2:AD2"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18455,7 +18463,7 @@
       </c>
       <c r="D2" s="90">
         <f>(C2/B2)^(1/3)-1</f>
-        <v>0.43948133016166602</v>
+        <v>0.43948133016166624</v>
       </c>
       <c r="E2" t="s">
         <v>272</v>
@@ -18468,7 +18476,7 @@
       </c>
       <c r="H2" s="90">
         <f>G2/F2-1</f>
-        <v>0.90804597701149403</v>
+        <v>0.90804597701149414</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -18483,7 +18491,7 @@
       </c>
       <c r="D3" s="90">
         <f t="shared" ref="D3:D26" si="0">(C3/B3)^(1/3)-1</f>
-        <v>0.43745003541220201</v>
+        <v>0.43745003541220151</v>
       </c>
       <c r="E3" t="s">
         <v>273</v>
@@ -18496,7 +18504,7 @@
       </c>
       <c r="H3" s="90">
         <f t="shared" ref="H3:H26" si="1">G3/F3-1</f>
-        <v>0.50373134328358204</v>
+        <v>0.50373134328358216</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -18511,7 +18519,7 @@
       </c>
       <c r="D4" s="90">
         <f t="shared" si="0"/>
-        <v>0.37345226256401798</v>
+        <v>0.37345226256401842</v>
       </c>
       <c r="E4" t="s">
         <v>274</v>
@@ -18524,7 +18532,7 @@
       </c>
       <c r="H4" s="90">
         <f t="shared" si="1"/>
-        <v>0.82820898731455606</v>
+        <v>0.82820898731455617</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -18539,7 +18547,7 @@
       </c>
       <c r="D5" s="90">
         <f t="shared" si="0"/>
-        <v>0.19660827469320299</v>
+        <v>0.19660827469320341</v>
       </c>
       <c r="E5" t="s">
         <v>275</v>
@@ -18552,7 +18560,7 @@
       </c>
       <c r="H5" s="90">
         <f t="shared" si="1"/>
-        <v>0.21966527196652699</v>
+        <v>0.21966527196652708</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -18567,7 +18575,7 @@
       </c>
       <c r="D6" s="90">
         <f t="shared" si="0"/>
-        <v>0.295627309055566</v>
+        <v>0.29562730905556611</v>
       </c>
       <c r="E6" t="s">
         <v>276</v>
@@ -18580,7 +18588,7 @@
       </c>
       <c r="H6" s="90">
         <f t="shared" si="1"/>
-        <v>0.315589353612167</v>
+        <v>0.31558935361216744</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -18595,7 +18603,7 @@
       </c>
       <c r="D7" s="90">
         <f t="shared" si="0"/>
-        <v>0.19585877326774001</v>
+        <v>0.19585877326774037</v>
       </c>
       <c r="E7" t="s">
         <v>277</v>
@@ -18608,7 +18616,7 @@
       </c>
       <c r="H7" s="90">
         <f t="shared" si="1"/>
-        <v>0.37561274509803899</v>
+        <v>0.3756127450980391</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -18623,7 +18631,7 @@
       </c>
       <c r="D8" s="90">
         <f t="shared" si="0"/>
-        <v>8.8471736106281507E-2</v>
+        <v>8.8471736106281451E-2</v>
       </c>
       <c r="E8" t="s">
         <v>278</v>
@@ -18636,7 +18644,7 @@
       </c>
       <c r="H8" s="90">
         <f t="shared" si="1"/>
-        <v>0.14057917888563001</v>
+        <v>0.14057917888563032</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -18651,7 +18659,7 @@
       </c>
       <c r="D9" s="90">
         <f t="shared" si="0"/>
-        <v>0.15675518451803699</v>
+        <v>0.15675518451803683</v>
       </c>
       <c r="E9" t="s">
         <v>279</v>
@@ -18664,7 +18672,7 @@
       </c>
       <c r="H9" s="90">
         <f t="shared" si="1"/>
-        <v>0.41787003610108298</v>
+        <v>0.4178700361010832</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -18679,7 +18687,7 @@
       </c>
       <c r="D10" s="90">
         <f t="shared" si="0"/>
-        <v>0.14523634718333001</v>
+        <v>0.14523634718333045</v>
       </c>
       <c r="E10" t="s">
         <v>280</v>
@@ -18692,7 +18700,7 @@
       </c>
       <c r="H10" s="90">
         <f t="shared" si="1"/>
-        <v>0.242299794661191</v>
+        <v>0.24229979466119089</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -18707,7 +18715,7 @@
       </c>
       <c r="D11" s="90">
         <f t="shared" si="0"/>
-        <v>0.18668687329363801</v>
+        <v>0.18668687329363753</v>
       </c>
       <c r="E11" t="s">
         <v>281</v>
@@ -18720,7 +18728,7 @@
       </c>
       <c r="H11" s="90">
         <f t="shared" si="1"/>
-        <v>0.26470588235294101</v>
+        <v>0.26470588235294112</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -18735,7 +18743,7 @@
       </c>
       <c r="D12" s="90">
         <f t="shared" si="0"/>
-        <v>0.17572165723677799</v>
+        <v>0.17572165723677768</v>
       </c>
       <c r="E12" t="s">
         <v>282</v>
@@ -18748,7 +18756,7 @@
       </c>
       <c r="H12" s="90">
         <f t="shared" si="1"/>
-        <v>-0.27927927927927898</v>
+        <v>-0.2792792792792792</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -18763,7 +18771,7 @@
       </c>
       <c r="D13" s="90">
         <f t="shared" si="0"/>
-        <v>4.0327167138589901E-2</v>
+        <v>4.0327167138589859E-2</v>
       </c>
       <c r="E13" t="s">
         <v>283</v>
@@ -18791,7 +18799,7 @@
       </c>
       <c r="D14" s="90">
         <f t="shared" si="0"/>
-        <v>0.127316248584224</v>
+        <v>0.12731624858422363</v>
       </c>
       <c r="E14" t="s">
         <v>284</v>
@@ -18804,7 +18812,7 @@
       </c>
       <c r="H14" s="90">
         <f t="shared" si="1"/>
-        <v>0.107573726541555</v>
+        <v>0.10757372654155484</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -18819,7 +18827,7 @@
       </c>
       <c r="D15" s="90">
         <f t="shared" si="0"/>
-        <v>0.15163183346768799</v>
+        <v>0.15163183346768783</v>
       </c>
       <c r="E15" t="s">
         <v>285</v>
@@ -18832,7 +18840,7 @@
       </c>
       <c r="H15" s="90">
         <f t="shared" si="1"/>
-        <v>0.10849056603773601</v>
+        <v>0.10849056603773599</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -18847,7 +18855,7 @@
       </c>
       <c r="D16" s="90">
         <f t="shared" si="0"/>
-        <v>0.118501337023027</v>
+        <v>0.11850133702302723</v>
       </c>
       <c r="E16" t="s">
         <v>286</v>
@@ -18860,7 +18868,7 @@
       </c>
       <c r="H16" s="90">
         <f t="shared" si="1"/>
-        <v>0.10774647887324</v>
+        <v>0.10774647887323963</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -18875,7 +18883,7 @@
       </c>
       <c r="D17" s="90">
         <f t="shared" si="0"/>
-        <v>6.0358052178632403E-2</v>
+        <v>6.0358052178632438E-2</v>
       </c>
       <c r="E17" t="s">
         <v>287</v>
@@ -18888,7 +18896,7 @@
       </c>
       <c r="H17" s="90">
         <f t="shared" si="1"/>
-        <v>-4.18743768693919E-3</v>
+        <v>-4.1874376869391883E-3</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -18903,7 +18911,7 @@
       </c>
       <c r="D18" s="90">
         <f t="shared" si="0"/>
-        <v>9.9172932019002694E-2</v>
+        <v>9.917293201900268E-2</v>
       </c>
       <c r="E18" t="s">
         <v>288</v>
@@ -18916,7 +18924,7 @@
       </c>
       <c r="H18" s="90">
         <f t="shared" si="1"/>
-        <v>8.0000000000000106E-3</v>
+        <v>8.0000000000000071E-3</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -18931,7 +18939,7 @@
       </c>
       <c r="D19" s="90">
         <f t="shared" si="0"/>
-        <v>2.4127390720476E-2</v>
+        <v>2.4127390720475983E-2</v>
       </c>
       <c r="E19" t="s">
         <v>289</v>
@@ -18959,7 +18967,7 @@
       </c>
       <c r="D20" s="90">
         <f t="shared" si="0"/>
-        <v>1.8206929812866601E-2</v>
+        <v>1.8206929812866646E-2</v>
       </c>
       <c r="E20" t="s">
         <v>290</v>
@@ -18972,7 +18980,7 @@
       </c>
       <c r="H20" s="90">
         <f t="shared" si="1"/>
-        <v>-3.9053254437869903E-2</v>
+        <v>-3.9053254437869889E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -19013,7 +19021,7 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" si="0"/>
-        <v>-1.9402028510212601</v>
+        <v>-1.9402028510212608</v>
       </c>
       <c r="E22" t="s">
         <v>292</v>
@@ -19039,7 +19047,7 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" si="0"/>
-        <v>-3.2454345993166598</v>
+        <v>-3.2454345993166576</v>
       </c>
       <c r="E23" t="s">
         <v>293</v>
@@ -19144,24 +19152,24 @@
       <c r="B2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="352" t="s">
+      <c r="C2" s="371" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="352"/>
-      <c r="E2" s="352"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="380" t="s">
+      <c r="G2" s="381" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="381"/>
+      <c r="H2" s="393"/>
       <c r="I2" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="382" t="s">
+      <c r="K2" s="383" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="383"/>
+      <c r="L2" s="394"/>
       <c r="M2" s="5" t="s">
         <v>89</v>
       </c>
@@ -19236,7 +19244,7 @@
       </c>
       <c r="M4" s="22">
         <f>65.8%-1</f>
-        <v>-0.34200000000000003</v>
+        <v>-0.34200000000000008</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
@@ -19312,7 +19320,7 @@
       </c>
       <c r="M6" s="22">
         <f>69.7%-1</f>
-        <v>-0.30299999999999999</v>
+        <v>-0.30299999999999994</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
@@ -19351,7 +19359,7 @@
       </c>
       <c r="M7" s="22">
         <f>71%-1</f>
-        <v>-0.28999999999999998</v>
+        <v>-0.29000000000000004</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
@@ -19388,7 +19396,7 @@
       </c>
       <c r="M8" s="22">
         <f>72.4%-1</f>
-        <v>-0.27600000000000002</v>
+        <v>-0.27599999999999991</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.3">
@@ -19635,20 +19643,20 @@
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="384" t="s">
+      <c r="B16" s="395" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="385"/>
-      <c r="D16" s="385"/>
-      <c r="E16" s="385"/>
-      <c r="F16" s="385"/>
-      <c r="G16" s="385"/>
-      <c r="H16" s="385"/>
-      <c r="I16" s="385"/>
-      <c r="J16" s="385"/>
-      <c r="K16" s="385"/>
-      <c r="L16" s="385"/>
-      <c r="M16" s="386"/>
+      <c r="C16" s="396"/>
+      <c r="D16" s="396"/>
+      <c r="E16" s="396"/>
+      <c r="F16" s="396"/>
+      <c r="G16" s="396"/>
+      <c r="H16" s="396"/>
+      <c r="I16" s="396"/>
+      <c r="J16" s="396"/>
+      <c r="K16" s="396"/>
+      <c r="L16" s="396"/>
+      <c r="M16" s="397"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B17" s="24" t="s">
@@ -19656,15 +19664,15 @@
       </c>
       <c r="C17" s="25">
         <f>AVERAGE(C4:C6)</f>
-        <v>2.6346097682150599E-2</v>
+        <v>2.6346097682150571E-2</v>
       </c>
       <c r="D17" s="25">
         <f>AVERAGE(D4:D6)</f>
-        <v>1.2644605886939501E-2</v>
+        <v>1.2644605886939527E-2</v>
       </c>
       <c r="E17" s="25">
         <f>AVERAGE(E4:E6)</f>
-        <v>1.7237019739619101E-2</v>
+        <v>1.7237019739619129E-2</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="27">
@@ -19689,7 +19697,7 @@
       </c>
       <c r="M17" s="30">
         <f>AVERAGE(M4:M6)</f>
-        <v>-0.30733333333333301</v>
+        <v>-0.30733333333333335</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -19706,7 +19714,7 @@
       </c>
       <c r="E18" s="25">
         <f t="shared" si="0"/>
-        <v>-8.5330349774372399E-2</v>
+        <v>-8.5330349774372372E-2</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="27" t="e">
@@ -19731,7 +19739,7 @@
       </c>
       <c r="M18" s="30">
         <f>AVERAGE(M7:M9)</f>
-        <v>-0.27800000000000002</v>
+        <v>-0.27799999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -19740,33 +19748,33 @@
       </c>
       <c r="C19" s="25">
         <f>AVERAGE(C10:C12)</f>
-        <v>-1.6666666666666701E-2</v>
+        <v>-1.6666666666666666E-2</v>
       </c>
       <c r="D19" s="25">
         <f>AVERAGE(D10:D12)</f>
-        <v>-7.5333333333333294E-2</v>
+        <v>-7.5333333333333335E-2</v>
       </c>
       <c r="E19" s="25">
         <f>AVERAGE(E10:E12)</f>
-        <v>-9.1999999999999998E-2</v>
+        <v>-9.2000000000000012E-2</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="27">
         <f>AVERAGE(G10:G12)</f>
-        <v>8.23333333333333E-2</v>
+        <v>8.2333333333333328E-2</v>
       </c>
       <c r="H19" s="26">
         <f>AVERAGE(H10:H12)</f>
-        <v>8.6666666666666697E-2</v>
+        <v>8.666666666666667E-2</v>
       </c>
       <c r="I19" s="28">
         <f>AVERAGE(I10:I12)</f>
-        <v>6.63333333333333E-2</v>
+        <v>6.6333333333333341E-2</v>
       </c>
       <c r="J19" s="32"/>
       <c r="K19" s="27">
         <f>AVERAGE(K10:K12)</f>
-        <v>-7.36666666666667E-2</v>
+        <v>-7.3666666666666672E-2</v>
       </c>
       <c r="L19" s="25">
         <f>AVERAGE(L10:L12)</f>
@@ -19774,7 +19782,7 @@
       </c>
       <c r="M19" s="30">
         <f>AVERAGE(M10:M12)</f>
-        <v>-0.21466666666666701</v>
+        <v>-0.21466666666666667</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -19783,7 +19791,7 @@
       </c>
       <c r="C20" s="25">
         <f>AVERAGE(C13:C15)</f>
-        <v>-1.36666666666667E-2</v>
+        <v>-1.3666666666666666E-2</v>
       </c>
       <c r="D20" s="25">
         <f>AVERAGE(D13:D15)</f>
@@ -19791,7 +19799,7 @@
       </c>
       <c r="E20" s="25">
         <f>AVERAGE(E13:E15)</f>
-        <v>-4.8000000000000001E-2</v>
+        <v>-4.7999999999999994E-2</v>
       </c>
       <c r="F20" s="33"/>
       <c r="G20" s="27">
@@ -19799,11 +19807,11 @@
       </c>
       <c r="H20" s="26">
         <f>AVERAGE(H13:H15)</f>
-        <v>7.6666666666666702E-2</v>
+        <v>7.6666666666666661E-2</v>
       </c>
       <c r="I20" s="28">
         <f>AVERAGE(I13:I15)</f>
-        <v>5.8000000000000003E-2</v>
+        <v>5.7999999999999996E-2</v>
       </c>
       <c r="J20" s="31"/>
       <c r="K20" s="27">
@@ -19811,28 +19819,28 @@
       </c>
       <c r="L20" s="25">
         <f>AVERAGE(L13:L15)</f>
-        <v>2.33333333333333E-2</v>
+        <v>2.3333333333333334E-2</v>
       </c>
       <c r="M20" s="30">
         <f>AVERAGE(M13:M15)</f>
-        <v>-0.209666666666667</v>
+        <v>-0.20966666666666667</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="387" t="s">
+      <c r="B21" s="398" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="388"/>
-      <c r="D21" s="388"/>
-      <c r="E21" s="388"/>
-      <c r="F21" s="388"/>
-      <c r="G21" s="388"/>
-      <c r="H21" s="388"/>
-      <c r="I21" s="388"/>
-      <c r="J21" s="388"/>
-      <c r="K21" s="388"/>
-      <c r="L21" s="388"/>
-      <c r="M21" s="389"/>
+      <c r="C21" s="399"/>
+      <c r="D21" s="399"/>
+      <c r="E21" s="399"/>
+      <c r="F21" s="399"/>
+      <c r="G21" s="399"/>
+      <c r="H21" s="399"/>
+      <c r="I21" s="399"/>
+      <c r="J21" s="399"/>
+      <c r="K21" s="399"/>
+      <c r="L21" s="399"/>
+      <c r="M21" s="400"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
@@ -19941,24 +19949,24 @@
       <c r="B29" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="352" t="s">
+      <c r="C29" s="371" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="352"/>
-      <c r="E29" s="390"/>
+      <c r="D29" s="371"/>
+      <c r="E29" s="380"/>
       <c r="F29" s="55"/>
-      <c r="G29" s="380" t="s">
+      <c r="G29" s="381" t="s">
         <v>60</v>
       </c>
-      <c r="H29" s="391"/>
+      <c r="H29" s="382"/>
       <c r="I29" s="56" t="s">
         <v>61</v>
       </c>
       <c r="J29" s="57"/>
-      <c r="K29" s="382" t="s">
+      <c r="K29" s="383" t="s">
         <v>62</v>
       </c>
-      <c r="L29" s="392"/>
+      <c r="L29" s="384"/>
       <c r="M29" s="5" t="s">
         <v>89</v>
       </c>
@@ -20110,20 +20118,20 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="49"/>
-      <c r="B34" s="393" t="s">
+      <c r="B34" s="385" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="394"/>
-      <c r="D34" s="394"/>
-      <c r="E34" s="394"/>
-      <c r="F34" s="395"/>
-      <c r="G34" s="394"/>
-      <c r="H34" s="394"/>
-      <c r="I34" s="394"/>
-      <c r="J34" s="395"/>
-      <c r="K34" s="394"/>
-      <c r="L34" s="394"/>
-      <c r="M34" s="396"/>
+      <c r="C34" s="386"/>
+      <c r="D34" s="386"/>
+      <c r="E34" s="386"/>
+      <c r="F34" s="387"/>
+      <c r="G34" s="386"/>
+      <c r="H34" s="386"/>
+      <c r="I34" s="386"/>
+      <c r="J34" s="387"/>
+      <c r="K34" s="386"/>
+      <c r="L34" s="386"/>
+      <c r="M34" s="388"/>
       <c r="N34" s="49"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -20164,20 +20172,20 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="49"/>
-      <c r="B36" s="397" t="s">
+      <c r="B36" s="389" t="s">
         <v>175</v>
       </c>
-      <c r="C36" s="398"/>
-      <c r="D36" s="398"/>
-      <c r="E36" s="398"/>
-      <c r="F36" s="399"/>
-      <c r="G36" s="398"/>
-      <c r="H36" s="398"/>
-      <c r="I36" s="398"/>
-      <c r="J36" s="399"/>
-      <c r="K36" s="398"/>
-      <c r="L36" s="398"/>
-      <c r="M36" s="400"/>
+      <c r="C36" s="390"/>
+      <c r="D36" s="390"/>
+      <c r="E36" s="390"/>
+      <c r="F36" s="391"/>
+      <c r="G36" s="390"/>
+      <c r="H36" s="390"/>
+      <c r="I36" s="390"/>
+      <c r="J36" s="391"/>
+      <c r="K36" s="390"/>
+      <c r="L36" s="390"/>
+      <c r="M36" s="392"/>
       <c r="N36" s="49"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -20321,16 +20329,16 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="10">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B21:M21"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="B34:M34"/>
     <mergeCell ref="B36:M36"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B21:M21"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20341,6 +20349,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+  <pixelatorList sheetStid="4"/>
+</pixelators>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <woSheetsProps>
     <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
@@ -20360,15 +20377,6 @@
     <bookSettings fileId="" isFilterShared="1" coreConquerUserId="" isAutoUpdatePaused="0" filterType="conn" isMergeTasksAutoUpdate="0" isInserPicAsAttachment="0"/>
   </woBookProps>
 </woProps>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-  <pixelatorList sheetStid="3"/>
-  <pixelatorList sheetStid="4"/>
-</pixelators>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20448,13 +20456,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
